--- a/data/trans_orig/P27_2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P27_2-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los fines de semana en 2007</t>
+          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los fines de semana en 2007 (tasa de respuesta: 94,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>100876</t>
+          <t>103737</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>142496</t>
+          <t>145861</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44525</t>
+          <t>45335</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73333</t>
+          <t>74057</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>154906</t>
+          <t>156408</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>207043</t>
+          <t>207889</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>245313</t>
+          <t>240209</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>299759</t>
+          <t>296219</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>174314</t>
+          <t>174026</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>223031</t>
+          <t>226599</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>429173</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>508377</t>
+          <t>506631</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>266129</t>
+          <t>265647</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>322131</t>
+          <t>322633</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>350737</t>
+          <t>354898</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>415568</t>
+          <t>416933</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>636945</t>
+          <t>633228</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>723461</t>
+          <t>722228</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,42%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>258499</t>
+          <t>254687</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>314736</t>
+          <t>312179</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>582137</t>
+          <t>578474</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>653294</t>
+          <t>650930</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>856389</t>
+          <t>856121</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>949746</t>
+          <t>946876</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,51%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>223972</t>
+          <t>220999</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>281809</t>
+          <t>280453</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>143126</t>
+          <t>143994</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>191088</t>
+          <t>192671</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>378663</t>
+          <t>380026</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>457575</t>
+          <t>455729</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>711219</t>
+          <t>713243</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>793822</t>
+          <t>793325</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>641958</t>
+          <t>638410</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>720216</t>
+          <t>713516</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1374531</t>
+          <t>1372159</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1486729</t>
+          <t>1491585</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,64%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>345539</t>
+          <t>347140</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>415426</t>
+          <t>417764</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>339544</t>
+          <t>343610</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>409338</t>
+          <t>410509</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>708883</t>
+          <t>707458</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>807223</t>
+          <t>805608</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>207857</t>
+          <t>209715</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>268294</t>
+          <t>269335</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>259556</t>
+          <t>260483</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>321309</t>
+          <t>319305</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>484788</t>
+          <t>489617</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>567252</t>
+          <t>569554</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42289</t>
+          <t>44282</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73186</t>
+          <t>73360</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29296</t>
+          <t>29955</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54083</t>
+          <t>53398</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>80136</t>
+          <t>80270</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>117581</t>
+          <t>119077</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>233173</t>
+          <t>232263</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>281087</t>
+          <t>279138</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181320</t>
+          <t>182300</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>224599</t>
+          <t>223672</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>428222</t>
+          <t>424646</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>490300</t>
+          <t>489009</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,66%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>101567</t>
+          <t>101665</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>143091</t>
+          <t>141192</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>125454</t>
+          <t>123772</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>165506</t>
+          <t>163050</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>233973</t>
+          <t>237321</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>292871</t>
+          <t>296031</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>72698</t>
+          <t>73055</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>107170</t>
+          <t>109367</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42838</t>
+          <t>41558</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>70415</t>
+          <t>71116</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>123478</t>
+          <t>123579</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>168047</t>
+          <t>169309</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,54%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>389288</t>
+          <t>391302</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>466944</t>
+          <t>469969</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>234875</t>
+          <t>236178</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>299242</t>
+          <t>297364</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>648353</t>
+          <t>645550</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>750053</t>
+          <t>747682</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1219424</t>
+          <t>1220083</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1329864</t>
+          <t>1329544</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1022865</t>
+          <t>1024648</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1132879</t>
+          <t>1133255</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2282017</t>
+          <t>2275752</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2434584</t>
+          <t>2434026</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,49%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>747697</t>
+          <t>749669</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>848249</t>
+          <t>846049</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>852377</t>
+          <t>853016</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>957369</t>
+          <t>951071</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1630126</t>
+          <t>1635900</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1769085</t>
+          <t>1783378</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>568437</t>
+          <t>570250</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>659594</t>
+          <t>662103</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>906965</t>
+          <t>910868</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1010862</t>
+          <t>1010245</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1505976</t>
+          <t>1506877</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1641932</t>
+          <t>1640378</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,94%</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los fines de semana en 2012</t>
+          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los fines de semana en 2012 (tasa de respuesta: 96,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15561</t>
+          <t>14983</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34767</t>
+          <t>34684</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9746</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25720</t>
+          <t>25572</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28924</t>
+          <t>28003</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54152</t>
+          <t>53161</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15407</t>
+          <t>15593</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36109</t>
+          <t>36034</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22406</t>
+          <t>22009</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45308</t>
+          <t>45366</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43149</t>
+          <t>43576</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73749</t>
+          <t>73830</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55625</t>
+          <t>56490</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>89988</t>
+          <t>88160</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>56433</t>
+          <t>55137</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>88887</t>
+          <t>89752</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>120637</t>
+          <t>118785</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>167049</t>
+          <t>167961</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>816412</t>
+          <t>817618</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>858369</t>
+          <t>856653</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1157572</t>
+          <t>1158082</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1199163</t>
+          <t>1198859</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1986508</t>
+          <t>1989438</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2048143</t>
+          <t>2048255</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,74%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44883</t>
+          <t>47410</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>75452</t>
+          <t>78055</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33126</t>
+          <t>33392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60436</t>
+          <t>59868</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,47 +3859,47 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>105366</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>87509</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>128274</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
           <t>3,57%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>105366</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>84885</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>124951</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>131458</t>
+          <t>127945</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>179517</t>
+          <t>176655</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96299</t>
+          <t>95708</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>136461</t>
+          <t>138215</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>234402</t>
+          <t>236034</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>301089</t>
+          <t>304232</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>244629</t>
+          <t>246972</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>307093</t>
+          <t>310326</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>191804</t>
+          <t>194688</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>251622</t>
+          <t>251287</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>459830</t>
+          <t>453204</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>542589</t>
+          <t>540168</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1370547</t>
+          <t>1366975</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1447553</t>
+          <t>1446064</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1272941</t>
+          <t>1274991</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1344961</t>
+          <t>1345655</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2671708</t>
+          <t>2665231</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2775366</t>
+          <t>2772878</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,2%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4072</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16383</t>
+          <t>15649</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15581</t>
+          <t>14721</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8988</t>
+          <t>8657</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24582</t>
+          <t>25710</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21201</t>
+          <t>21648</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43755</t>
+          <t>44199</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17669</t>
+          <t>18940</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40926</t>
+          <t>41844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>45251</t>
+          <t>45226</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>75493</t>
+          <t>75419</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64811</t>
+          <t>65647</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97792</t>
+          <t>98233</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>48876</t>
+          <t>49149</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79911</t>
+          <t>81133</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>122118</t>
+          <t>122931</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>169509</t>
+          <t>170118</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>325999</t>
+          <t>328028</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>366917</t>
+          <t>365597</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>320097</t>
+          <t>320519</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>357050</t>
+          <t>357188</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>658354</t>
+          <t>661854</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>713491</t>
+          <t>712906</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,62%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74301</t>
+          <t>74706</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>112287</t>
+          <t>112876</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53271</t>
+          <t>52892</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>86928</t>
+          <t>84673</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>134872</t>
+          <t>136263</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>184513</t>
+          <t>186343</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>181409</t>
+          <t>180596</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>238585</t>
+          <t>237173</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>151148</t>
+          <t>150561</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>203474</t>
+          <t>205092</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>343464</t>
+          <t>347863</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>421413</t>
+          <t>426216</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>389812</t>
+          <t>389442</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>468452</t>
+          <t>466202</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>321547</t>
+          <t>323645</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>399759</t>
+          <t>398906</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>732439</t>
+          <t>726313</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>837914</t>
+          <t>837389</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2544379</t>
+          <t>2547080</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2645782</t>
+          <t>2642664</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2781668</t>
+          <t>2781329</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2874346</t>
+          <t>2873588</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5357883</t>
+          <t>5359739</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5486492</t>
+          <t>5492170</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,29%</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los fines de semana en 2016</t>
+          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los fines de semana en 2016 (tasa de respuesta: 97,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15158</t>
+          <t>15185</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34594</t>
+          <t>34729</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13338</t>
+          <t>13919</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33003</t>
+          <t>34381</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35016</t>
+          <t>33047</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61993</t>
+          <t>61762</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29579</t>
+          <t>29775</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54593</t>
+          <t>53999</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34347</t>
+          <t>35187</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62285</t>
+          <t>64605</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72410</t>
+          <t>71456</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>107571</t>
+          <t>108381</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>74190</t>
+          <t>72263</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>108842</t>
+          <t>108909</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52543</t>
+          <t>51637</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>85121</t>
+          <t>85034</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>133317</t>
+          <t>133374</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>182185</t>
+          <t>182541</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>553842</t>
+          <t>553411</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>596312</t>
+          <t>598249</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>793608</t>
+          <t>798114</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>841677</t>
+          <t>841357</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1363585</t>
+          <t>1361377</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1425414</t>
+          <t>1425242</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,47%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73314</t>
+          <t>72461</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>111936</t>
+          <t>112811</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63769</t>
+          <t>64630</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>99417</t>
+          <t>100786</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>146978</t>
+          <t>147849</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>200408</t>
+          <t>202773</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>177624</t>
+          <t>175448</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>231214</t>
+          <t>229812</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>150754</t>
+          <t>152130</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>202836</t>
+          <t>203564</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>340022</t>
+          <t>344815</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>417610</t>
+          <t>417805</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>383231</t>
+          <t>379847</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>456045</t>
+          <t>452394</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>353707</t>
+          <t>353780</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>421930</t>
+          <t>424915</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>752350</t>
+          <t>758515</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>856699</t>
+          <t>856247</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1283786</t>
+          <t>1285412</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1371205</t>
+          <t>1374331</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1260645</t>
+          <t>1258393</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1340719</t>
+          <t>1345508</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2572024</t>
+          <t>2572134</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2695415</t>
+          <t>2691933</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,55%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5679</t>
+          <t>5057</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19417</t>
+          <t>19099</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>12563</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29867</t>
+          <t>29601</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20469</t>
+          <t>20590</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>43297</t>
+          <t>41712</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25195</t>
+          <t>26055</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51153</t>
+          <t>50690</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21229</t>
+          <t>20776</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42772</t>
+          <t>42093</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>50753</t>
+          <t>50478</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>83880</t>
+          <t>84485</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72204</t>
+          <t>69971</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>105191</t>
+          <t>105728</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>80118</t>
+          <t>82809</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>117582</t>
+          <t>119194</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>162876</t>
+          <t>161852</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>214202</t>
+          <t>212169</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,79%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>379782</t>
+          <t>377808</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>422663</t>
+          <t>418156</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>369157</t>
+          <t>366826</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>410938</t>
+          <t>406982</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>754471</t>
+          <t>755405</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>818280</t>
+          <t>816156</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,11%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>106408</t>
+          <t>104453</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>152561</t>
+          <t>152357</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,82 +7469,82 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>122477</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>102694</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>145641</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>248126</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>217377</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>281977</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>3,68%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>3,22%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>122477</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>99390</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>145712</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>4,24%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>248126</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>220025</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>279275</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249601</t>
+          <t>249353</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>317374</t>
+          <t>315403</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>224545</t>
+          <t>223102</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>284351</t>
+          <t>285788</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>491905</t>
+          <t>488174</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>581559</t>
+          <t>577506</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>550887</t>
+          <t>551300</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>640541</t>
+          <t>642169</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>517374</t>
+          <t>512388</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>600897</t>
+          <t>597190</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1086514</t>
+          <t>1095960</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1209889</t>
+          <t>1221660</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,11%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2251729</t>
+          <t>2252326</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2355033</t>
+          <t>2354980</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2456483</t>
+          <t>2459855</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2563205</t>
+          <t>2567062</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4740643</t>
+          <t>4740879</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4887942</t>
+          <t>4885601</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,43%</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los fines de semana en 2023</t>
+          <t>Población según el tiempo que pasa en ambientes cargados de humo de tabaco durante los fines de semana en 2023 (tasa de respuesta: 99,59%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17148</t>
+          <t>17159</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5741</t>
+          <t>5443</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15872</t>
+          <t>16252</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13115</t>
+          <t>12984</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27830</t>
+          <t>28066</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23370</t>
+          <t>23266</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48193</t>
+          <t>47558</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12019</t>
+          <t>12315</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24355</t>
+          <t>24573</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40338</t>
+          <t>39876</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67991</t>
+          <t>66913</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42515</t>
+          <t>42204</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>74557</t>
+          <t>74645</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34678</t>
+          <t>35221</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>57853</t>
+          <t>60457</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>83570</t>
+          <t>83044</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>123279</t>
+          <t>124408</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>394844</t>
+          <t>393948</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>432658</t>
+          <t>432958</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>663524</t>
+          <t>659976</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>689503</t>
+          <t>689486</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8643,7 +8643,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1064980</t>
+          <t>1067080</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1114600</t>
+          <t>1116643</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,34%</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11340</t>
+          <t>12287</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34464</t>
+          <t>36070</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14043</t>
+          <t>14415</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36932</t>
+          <t>36769</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>32035</t>
+          <t>29409</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>62703</t>
+          <t>63174</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>107826</t>
+          <t>111774</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>198231</t>
+          <t>200724</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79020</t>
+          <t>80537</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>132907</t>
+          <t>134972</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>208786</t>
+          <t>214202</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>319263</t>
+          <t>319608</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>199655</t>
+          <t>208763</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>349058</t>
+          <t>347710</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>171360</t>
+          <t>170464</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>275401</t>
+          <t>277366</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>411072</t>
+          <t>425184</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>600381</t>
+          <t>605925</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1735017</t>
+          <t>1732324</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1965756</t>
+          <t>1967881</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1804496</t>
+          <t>1797466</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1968854</t>
+          <t>1957357</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3569666</t>
+          <t>3557155</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3854253</t>
+          <t>3835372</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,0%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>1687</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12403</t>
+          <t>11861</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10415</t>
+          <t>10152</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>5314</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19069</t>
+          <t>18813</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21392</t>
+          <t>21022</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46404</t>
+          <t>46657</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19395</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38233</t>
+          <t>40294</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>47201</t>
+          <t>45668</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>77481</t>
+          <t>77389</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>59013</t>
+          <t>58954</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96070</t>
+          <t>96307</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70461</t>
+          <t>72040</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>102223</t>
+          <t>103204</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>140424</t>
+          <t>137821</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>189373</t>
+          <t>187430</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>502848</t>
+          <t>502532</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>544541</t>
+          <t>545757</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>522894</t>
+          <t>520013</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>558036</t>
+          <t>555956</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1034789</t>
+          <t>1038807</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1089146</t>
+          <t>1092194</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,25%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25054</t>
+          <t>25005</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52536</t>
+          <t>54220</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27120</t>
+          <t>26263</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50622</t>
+          <t>51250</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56809</t>
+          <t>56636</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>95241</t>
+          <t>93829</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>169694</t>
+          <t>170551</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268019</t>
+          <t>264514</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>125159</t>
+          <t>125923</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>181850</t>
+          <t>183646</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>320564</t>
+          <t>325736</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>435856</t>
+          <t>430318</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>331186</t>
+          <t>325218</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>485438</t>
+          <t>479497</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>305259</t>
+          <t>296393</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>409490</t>
+          <t>408820</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>685568</t>
+          <t>695589</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>868663</t>
+          <t>877551</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2667121</t>
+          <t>2676803</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2907802</t>
+          <t>2905547</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3022027</t>
+          <t>3016871</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3170009</t>
+          <t>3176655</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5721937</t>
+          <t>5711606</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5992014</t>
+          <t>5979268</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,54%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P27_2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P27_2-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>103737</t>
+          <t>104576</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>145861</t>
+          <t>145879</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45335</t>
+          <t>44302</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74057</t>
+          <t>73685</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>156408</t>
+          <t>158777</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>207889</t>
+          <t>209834</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>240209</t>
+          <t>242150</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>296219</t>
+          <t>296858</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>174026</t>
+          <t>173128</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>226599</t>
+          <t>226989</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>431602</t>
+          <t>430562</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>506631</t>
+          <t>507922</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,8%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>265647</t>
+          <t>268109</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>322633</t>
+          <t>324248</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>354898</t>
+          <t>353309</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>416933</t>
+          <t>417673</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>633228</t>
+          <t>637811</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>722228</t>
+          <t>720114</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,33%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>254687</t>
+          <t>259160</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>312179</t>
+          <t>315910</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>578474</t>
+          <t>580174</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>650930</t>
+          <t>650646</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>856121</t>
+          <t>854269</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>946876</t>
+          <t>942750</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,32%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>220999</t>
+          <t>222560</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>280453</t>
+          <t>282953</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>143994</t>
+          <t>144603</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>192671</t>
+          <t>191244</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>380026</t>
+          <t>381171</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>455729</t>
+          <t>453024</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>713243</t>
+          <t>707070</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>793325</t>
+          <t>792052</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>638410</t>
+          <t>644989</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>713516</t>
+          <t>720301</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1372159</t>
+          <t>1376326</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1491585</t>
+          <t>1486581</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,48%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>347140</t>
+          <t>348045</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>417764</t>
+          <t>415234</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>343610</t>
+          <t>341890</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>410509</t>
+          <t>410268</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>707458</t>
+          <t>707938</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>805608</t>
+          <t>805575</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>209715</t>
+          <t>211207</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>269335</t>
+          <t>268202</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>260483</t>
+          <t>257726</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>319305</t>
+          <t>319583</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>489617</t>
+          <t>489353</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>569554</t>
+          <t>572053</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44282</t>
+          <t>43001</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73360</t>
+          <t>72498</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29955</t>
+          <t>29116</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53398</t>
+          <t>53516</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>80270</t>
+          <t>79542</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>119077</t>
+          <t>117804</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>232263</t>
+          <t>233786</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>279138</t>
+          <t>283134</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>182300</t>
+          <t>182337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>223672</t>
+          <t>225644</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>424646</t>
+          <t>426635</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>489009</t>
+          <t>490410</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,8%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>101665</t>
+          <t>100488</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>141192</t>
+          <t>142270</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>123772</t>
+          <t>123647</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>163050</t>
+          <t>164581</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>237321</t>
+          <t>236066</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>296031</t>
+          <t>292962</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73055</t>
+          <t>73018</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>109367</t>
+          <t>108058</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41558</t>
+          <t>41314</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71116</t>
+          <t>70370</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>123579</t>
+          <t>124189</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>169309</t>
+          <t>168817</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>391302</t>
+          <t>393786</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>469969</t>
+          <t>471211</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>236178</t>
+          <t>234578</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>297364</t>
+          <t>295878</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>645550</t>
+          <t>641636</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>747682</t>
+          <t>744661</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1220083</t>
+          <t>1227795</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1329544</t>
+          <t>1334265</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1024648</t>
+          <t>1028513</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1133255</t>
+          <t>1131020</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2275752</t>
+          <t>2281359</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2434026</t>
+          <t>2440692</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,6%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>749669</t>
+          <t>745061</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>846049</t>
+          <t>847197</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>853016</t>
+          <t>854726</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>951071</t>
+          <t>951844</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1635900</t>
+          <t>1624444</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1783378</t>
+          <t>1770962</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,01%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>570250</t>
+          <t>570737</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>662103</t>
+          <t>660272</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>910868</t>
+          <t>907407</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1010245</t>
+          <t>1018057</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1506877</t>
+          <t>1501433</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1640378</t>
+          <t>1643285</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14983</t>
+          <t>14589</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34684</t>
+          <t>34637</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9296</t>
+          <t>9861</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25572</t>
+          <t>25337</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28003</t>
+          <t>27970</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53161</t>
+          <t>52580</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15593</t>
+          <t>16321</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36034</t>
+          <t>37132</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22009</t>
+          <t>22597</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45366</t>
+          <t>45949</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43576</t>
+          <t>42687</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73830</t>
+          <t>73937</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56490</t>
+          <t>57579</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>88160</t>
+          <t>91767</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>55137</t>
+          <t>54401</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>89752</t>
+          <t>89576</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118785</t>
+          <t>122817</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>167961</t>
+          <t>168680</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>817618</t>
+          <t>816314</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>856653</t>
+          <t>858081</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1158082</t>
+          <t>1156205</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1198859</t>
+          <t>1200576</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1989438</t>
+          <t>1987273</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2048255</t>
+          <t>2046236</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,65%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47410</t>
+          <t>46246</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>78055</t>
+          <t>75946</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33392</t>
+          <t>33404</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59868</t>
+          <t>61051</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>87509</t>
+          <t>85757</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>128274</t>
+          <t>124901</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>127945</t>
+          <t>129934</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>176655</t>
+          <t>177726</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>95708</t>
+          <t>97118</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>138215</t>
+          <t>139033</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>236034</t>
+          <t>240680</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>304232</t>
+          <t>302103</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>246972</t>
+          <t>244545</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310326</t>
+          <t>306253</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>194688</t>
+          <t>194073</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>251287</t>
+          <t>251228</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>453204</t>
+          <t>451971</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>540168</t>
+          <t>541827</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1366975</t>
+          <t>1368326</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1446064</t>
+          <t>1448417</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1274991</t>
+          <t>1273222</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1345655</t>
+          <t>1343599</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2665231</t>
+          <t>2666044</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2772878</t>
+          <t>2769931</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,12%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15649</t>
+          <t>15873</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14721</t>
+          <t>14240</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8657</t>
+          <t>8697</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25710</t>
+          <t>25492</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21648</t>
+          <t>20897</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>44199</t>
+          <t>42997</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18940</t>
+          <t>19062</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>41844</t>
+          <t>41816</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>45226</t>
+          <t>45019</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>75419</t>
+          <t>76455</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65647</t>
+          <t>65472</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98233</t>
+          <t>99676</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49149</t>
+          <t>49487</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>81133</t>
+          <t>81647</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>122931</t>
+          <t>124510</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>170118</t>
+          <t>170152</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>328028</t>
+          <t>330378</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>365597</t>
+          <t>367443</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>320519</t>
+          <t>319916</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>357188</t>
+          <t>357523</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>661854</t>
+          <t>659850</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>712906</t>
+          <t>711729</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,49%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74706</t>
+          <t>74770</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>112876</t>
+          <t>111110</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52892</t>
+          <t>52843</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>84673</t>
+          <t>86325</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>136263</t>
+          <t>133977</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>186343</t>
+          <t>187365</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>180596</t>
+          <t>180872</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237173</t>
+          <t>240248</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>150561</t>
+          <t>151356</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>205092</t>
+          <t>202344</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>347863</t>
+          <t>343735</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>426216</t>
+          <t>425720</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>389442</t>
+          <t>387647</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>466202</t>
+          <t>463400</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>323645</t>
+          <t>324463</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>398906</t>
+          <t>398401</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,47 +5223,47 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
+          <t>11,61%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>785169</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>728804</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>842224</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
           <t>11,62%</t>
         </is>
       </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>748</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>785169</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>726313</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>837389</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>11,62%</t>
-        </is>
-      </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2547080</t>
+          <t>2550029</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2642664</t>
+          <t>2644756</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2781329</t>
+          <t>2779718</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2873588</t>
+          <t>2872377</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5359739</t>
+          <t>5358354</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5492170</t>
+          <t>5491420</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,28%</t>
         </is>
       </c>
     </row>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15185</t>
+          <t>15687</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34729</t>
+          <t>33844</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13919</t>
+          <t>14817</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34381</t>
+          <t>34118</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33047</t>
+          <t>34192</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61762</t>
+          <t>62525</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29775</t>
+          <t>30129</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53999</t>
+          <t>55162</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35187</t>
+          <t>34339</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64605</t>
+          <t>61253</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>71456</t>
+          <t>72421</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>108381</t>
+          <t>108920</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>72263</t>
+          <t>72347</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>108909</t>
+          <t>110017</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51637</t>
+          <t>53086</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>85034</t>
+          <t>87456</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>133374</t>
+          <t>135483</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>182541</t>
+          <t>183638</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>553411</t>
+          <t>551758</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>598249</t>
+          <t>596447</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>798114</t>
+          <t>796151</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>841357</t>
+          <t>841905</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1361377</t>
+          <t>1363787</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1425242</t>
+          <t>1424295</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,41%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72461</t>
+          <t>73820</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>112811</t>
+          <t>112962</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>64630</t>
+          <t>63871</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>100786</t>
+          <t>98187</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>147849</t>
+          <t>148925</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>202773</t>
+          <t>199652</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>175448</t>
+          <t>175309</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>229812</t>
+          <t>232721</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>152130</t>
+          <t>152453</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>203564</t>
+          <t>201283</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>344815</t>
+          <t>342036</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>417805</t>
+          <t>414839</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>379847</t>
+          <t>380540</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452394</t>
+          <t>452519</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>353780</t>
+          <t>355088</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>424915</t>
+          <t>425493</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>758515</t>
+          <t>754961</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>856247</t>
+          <t>856628</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1285412</t>
+          <t>1284280</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1374331</t>
+          <t>1370701</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1258393</t>
+          <t>1261101</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1345508</t>
+          <t>1341136</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2572134</t>
+          <t>2567464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2691933</t>
+          <t>2688485</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,46%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19099</t>
+          <t>19655</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12563</t>
+          <t>11718</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29601</t>
+          <t>29269</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20590</t>
+          <t>20615</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41712</t>
+          <t>42244</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26055</t>
+          <t>24759</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50690</t>
+          <t>50680</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20776</t>
+          <t>21209</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42093</t>
+          <t>42213</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>50478</t>
+          <t>52181</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>84485</t>
+          <t>84248</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69971</t>
+          <t>72066</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>105728</t>
+          <t>106019</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>82809</t>
+          <t>79039</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>119194</t>
+          <t>117940</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>161852</t>
+          <t>162758</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>212169</t>
+          <t>212031</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,77%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>377808</t>
+          <t>376347</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>418156</t>
+          <t>418462</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>366826</t>
+          <t>367298</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>406982</t>
+          <t>412817</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>755405</t>
+          <t>757920</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>816156</t>
+          <t>816605</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,15%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>104453</t>
+          <t>104099</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>152357</t>
+          <t>150452</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>102694</t>
+          <t>101964</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>145641</t>
+          <t>147267</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>217377</t>
+          <t>218388</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>281977</t>
+          <t>280662</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249353</t>
+          <t>248856</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>315403</t>
+          <t>314760</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>223102</t>
+          <t>222089</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>285788</t>
+          <t>285184</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>488174</t>
+          <t>489556</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>577506</t>
+          <t>581905</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>551300</t>
+          <t>551691</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>642169</t>
+          <t>646753</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>512388</t>
+          <t>512159</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>597190</t>
+          <t>599488</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1095960</t>
+          <t>1093226</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1221660</t>
+          <t>1214163</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2252326</t>
+          <t>2254222</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2354980</t>
+          <t>2358980</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2459855</t>
+          <t>2459851</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2567062</t>
+          <t>2561390</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4740879</t>
+          <t>4741562</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4885601</t>
+          <t>4882815</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,39%</t>
         </is>
       </c>
     </row>
@@ -8249,32 +8249,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9705</t>
+          <t>12412</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5796</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17159</t>
+          <t>21393</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8284,32 +8284,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9572</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16252</t>
+          <t>17928</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8319,32 +8319,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>19277</t>
+          <t>23202</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12984</t>
+          <t>16068</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28066</t>
+          <t>34053</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -8362,32 +8362,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33728</t>
+          <t>34391</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23266</t>
+          <t>24656</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47558</t>
+          <t>47446</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8397,32 +8397,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17684</t>
+          <t>18643</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12315</t>
+          <t>12945</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24573</t>
+          <t>25414</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8432,32 +8432,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>51412</t>
+          <t>53035</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39876</t>
+          <t>40004</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66913</t>
+          <t>67043</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -8475,32 +8475,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55969</t>
+          <t>63453</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42204</t>
+          <t>49216</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>74645</t>
+          <t>81696</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8510,32 +8510,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45263</t>
+          <t>47289</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35221</t>
+          <t>37542</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60457</t>
+          <t>61676</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8545,32 +8545,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>101232</t>
+          <t>110742</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>83044</t>
+          <t>91774</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>124408</t>
+          <t>134812</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>414806</t>
+          <t>467269</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>393948</t>
+          <t>446423</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>432958</t>
+          <t>485346</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>677279</t>
+          <t>739305</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>659976</t>
+          <t>724044</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>689486</t>
+          <t>752381</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8658,32 +8658,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1092086</t>
+          <t>1206575</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1067080</t>
+          <t>1181016</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1116643</t>
+          <t>1232438</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,44%</t>
         </is>
       </c>
     </row>
@@ -8701,17 +8701,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>514208</t>
+          <t>577525</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>514208</t>
+          <t>577525</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514208</t>
+          <t>577525</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>749798</t>
+          <t>816027</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>749798</t>
+          <t>816027</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>749798</t>
+          <t>816027</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1264006</t>
+          <t>1393553</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1264006</t>
+          <t>1393553</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1264006</t>
+          <t>1393553</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8818,102 +8818,102 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21001</t>
+          <t>25501</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12287</t>
+          <t>14703</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36070</t>
+          <t>40500</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>29421</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>18357</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>41435</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>54922</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>40270</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>75553</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>0,92%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>23392</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>14415</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>36769</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>44393</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>29409</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>63174</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -8931,32 +8931,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>159923</t>
+          <t>162070</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>111774</t>
+          <t>134821</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>200724</t>
+          <t>194706</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8966,32 +8966,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>109875</t>
+          <t>114937</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80537</t>
+          <t>98482</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>134972</t>
+          <t>135692</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9001,32 +9001,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>269797</t>
+          <t>277006</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>214202</t>
+          <t>241893</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>319608</t>
+          <t>314591</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>292560</t>
+          <t>301426</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>208763</t>
+          <t>261775</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>347710</t>
+          <t>340680</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9079,32 +9079,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>235232</t>
+          <t>258248</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>170464</t>
+          <t>232476</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>277366</t>
+          <t>287885</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9114,32 +9114,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>527792</t>
+          <t>559674</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>425184</t>
+          <t>515794</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>605925</t>
+          <t>611333</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1809609</t>
+          <t>1733675</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1732324</t>
+          <t>1683395</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1967881</t>
+          <t>1778717</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1860536</t>
+          <t>1755901</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1797466</t>
+          <t>1719453</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1957357</t>
+          <t>1788540</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3670146</t>
+          <t>3489577</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3557155</t>
+          <t>3428273</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3835372</t>
+          <t>3545678</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>80,93%</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2283092</t>
+          <t>2222672</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2283092</t>
+          <t>2222672</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2283092</t>
+          <t>2222672</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2229035</t>
+          <t>2158506</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2229035</t>
+          <t>2158506</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2229035</t>
+          <t>2158506</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4512128</t>
+          <t>4381179</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4512128</t>
+          <t>4381179</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4512128</t>
+          <t>4381179</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9387,32 +9387,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>5460</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1687</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11861</t>
+          <t>12251</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9422,32 +9422,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10152</t>
+          <t>10995</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9457,22 +9457,22 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>10149</t>
+          <t>10494</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18813</t>
+          <t>19857</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -9500,32 +9500,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31986</t>
+          <t>32782</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21022</t>
+          <t>22372</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46657</t>
+          <t>48195</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9535,32 +9535,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28232</t>
+          <t>30063</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>21311</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40294</t>
+          <t>42451</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9570,32 +9570,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>60219</t>
+          <t>62844</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>45668</t>
+          <t>49141</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>77389</t>
+          <t>82202</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -9613,32 +9613,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>75844</t>
+          <t>82120</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>58954</t>
+          <t>64631</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96307</t>
+          <t>104860</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9648,32 +9648,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>85927</t>
+          <t>89122</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72040</t>
+          <t>74356</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>103204</t>
+          <t>105495</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9683,32 +9683,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>161771</t>
+          <t>171242</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>137821</t>
+          <t>148397</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>187430</t>
+          <t>196744</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -9726,32 +9726,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>524599</t>
+          <t>590043</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>502532</t>
+          <t>565419</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>545757</t>
+          <t>612177</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9761,32 +9761,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>539607</t>
+          <t>607965</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>520013</t>
+          <t>588379</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>555956</t>
+          <t>624767</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9796,32 +9796,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1064207</t>
+          <t>1198008</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1038807</t>
+          <t>1167937</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1092194</t>
+          <t>1223686</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,83%</t>
         </is>
       </c>
     </row>
@@ -9839,17 +9839,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>637662</t>
+          <t>710405</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>637662</t>
+          <t>710405</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>637662</t>
+          <t>710405</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>658682</t>
+          <t>732183</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>658682</t>
+          <t>732183</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>658682</t>
+          <t>732183</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9909,17 +9909,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1296345</t>
+          <t>1442588</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1296345</t>
+          <t>1442588</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1296345</t>
+          <t>1442588</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9956,32 +9956,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>35939</t>
+          <t>43373</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25005</t>
+          <t>31510</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54220</t>
+          <t>65518</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9991,32 +9991,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>37880</t>
+          <t>45244</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26263</t>
+          <t>34863</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51250</t>
+          <t>61969</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10026,32 +10026,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>73819</t>
+          <t>88617</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56636</t>
+          <t>70347</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>93829</t>
+          <t>111455</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -10069,32 +10069,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>225637</t>
+          <t>229243</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>170551</t>
+          <t>198951</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264514</t>
+          <t>268337</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10104,32 +10104,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>155791</t>
+          <t>163642</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>125923</t>
+          <t>142253</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>183646</t>
+          <t>191569</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>381428</t>
+          <t>392885</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>325736</t>
+          <t>354922</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>430318</t>
+          <t>436720</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -10182,32 +10182,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>424373</t>
+          <t>446999</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>325218</t>
+          <t>409699</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>479497</t>
+          <t>500772</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10217,32 +10217,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>366421</t>
+          <t>394659</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>296393</t>
+          <t>364541</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>408820</t>
+          <t>430425</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10252,32 +10252,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>790794</t>
+          <t>841658</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>695589</t>
+          <t>783377</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>877551</t>
+          <t>900450</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -10295,32 +10295,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2749014</t>
+          <t>2790987</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2676803</t>
+          <t>2733009</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2905547</t>
+          <t>2841688</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10330,32 +10330,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3077424</t>
+          <t>3103172</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3016871</t>
+          <t>3062490</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3176655</t>
+          <t>3143148</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10365,32 +10365,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>5826438</t>
+          <t>5894159</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5711606</t>
+          <t>5823989</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5979268</t>
+          <t>5966445</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>82,67%</t>
         </is>
       </c>
     </row>
@@ -10408,17 +10408,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3434962</t>
+          <t>3510602</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3434962</t>
+          <t>3510602</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3434962</t>
+          <t>3510602</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3637516</t>
+          <t>3706717</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3637516</t>
+          <t>3706717</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3637516</t>
+          <t>3706717</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7072478</t>
+          <t>7217319</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7072478</t>
+          <t>7217319</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7072478</t>
+          <t>7217319</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
